--- a/ClosedXML.Tests/Resource/Examples/Misc/LambdaExpressions.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/LambdaExpressions.xlsx
@@ -98,31 +98,31 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right/>
       <top style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -130,45 +130,45 @@
       <left/>
       <right/>
       <top style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right/>
       <top/>
       <bottom style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -177,18 +177,18 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
